--- a/StructureDefinition-Laboratorieanalys-Aktivitet.xlsx
+++ b/StructureDefinition-Laboratorieanalys-Aktivitet.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:41:45+00:00</t>
+    <t>2026-09-18T09:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Laboratorieanalys-Aktivitet.xlsx
+++ b/StructureDefinition-Laboratorieanalys-Aktivitet.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="123">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T09:59:15+00:00</t>
+    <t>2026-09-18T10:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Supporting logical model generated from gloo4.xmi (source class: Laboratorieanalys : Aktivitet).</t>
+    <t>Klassen Laboratorieanalys håller information om en analys</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -263,6 +263,9 @@
     <t>Source attribute: id; renamed from reserved FSH name 'id'</t>
   </si>
   <si>
+    <t>Angivelse av identitetsbeteckning för en laboratorieanalys.</t>
+  </si>
+  <si>
     <t>Laboratorieanalys-Aktivitet.status</t>
   </si>
   <si>
@@ -273,6 +276,9 @@
     <t>Source attribute: status</t>
   </si>
   <si>
+    <t>Kod för analysens status.</t>
+  </si>
+  <si>
     <t>Laboratorieanalys-Aktivitet.kod</t>
   </si>
   <si>
@@ -283,6 +289,10 @@
     <t>Source attribute: kod</t>
   </si>
   <si>
+    <t>Kod för den typ av analys som utförts.
+Om kod inte kan anges från nationellt urval kan originalText användas för textalternativ.</t>
+  </si>
+  <si>
     <t>Laboratorieanalys-Aktivitet.tid</t>
   </si>
   <si>
@@ -293,10 +303,17 @@
     <t>Source attribute: tid</t>
   </si>
   <si>
+    <t>Angivelse av tidpunkt då analysen utfördes.</t>
+  </si>
+  <si>
     <t>Laboratorieanalys-Aktivitet.metod</t>
   </si>
   <si>
     <t>Source attribute: metod</t>
+  </si>
+  <si>
+    <t>Kod för den typ av tillvägagångssätt för utförandet av analysen som avses.
+Om kod inte kan anges från nationellt urval kan originalText användas för textalternativ.</t>
   </si>
   <si>
     <t>Laboratorieanalys-Aktivitet.kommentar</t>
@@ -309,6 +326,9 @@
     <t>Source attribute: kommentar</t>
   </si>
   <si>
+    <t>Angivelse av kommentar för en enskild analys.</t>
+  </si>
+  <si>
     <t>Laboratorieanalys-Aktivitet.ackrediteradMetod</t>
   </si>
   <si>
@@ -317,6 +337,9 @@
   </si>
   <si>
     <t>Source attribute: ackrediterad metod</t>
+  </si>
+  <si>
+    <t>Angivelse av om analysmetoden är ackrediterad eller inte.</t>
   </si>
   <si>
     <t>Laboratorieanalys-Aktivitet.bestarAv</t>
@@ -958,7 +981,7 @@
         <v>81</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1026,10 +1049,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1052,13 +1075,13 @@
         <v>20</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1109,7 +1132,7 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>79</v>
@@ -1126,10 +1149,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1152,13 +1175,13 @@
         <v>20</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1209,7 +1232,7 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>79</v>
@@ -1226,10 +1249,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1252,13 +1275,13 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1309,7 +1332,7 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>73</v>
@@ -1326,10 +1349,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1352,13 +1375,13 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1409,7 +1432,7 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>73</v>
@@ -1426,10 +1449,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1452,13 +1475,13 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1509,7 +1532,7 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>73</v>
@@ -1526,10 +1549,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1552,13 +1575,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1609,7 +1632,7 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>73</v>
@@ -1626,10 +1649,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1652,13 +1675,13 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1709,7 +1732,7 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -1726,10 +1749,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1752,13 +1775,13 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1809,7 +1832,7 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>73</v>
@@ -1826,10 +1849,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1852,13 +1875,13 @@
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1909,7 +1932,7 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>73</v>
@@ -1926,10 +1949,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -1952,13 +1975,13 @@
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2009,7 +2032,7 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>73</v>
@@ -2026,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2052,13 +2075,13 @@
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2109,7 +2132,7 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>73</v>
@@ -2126,10 +2149,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2152,13 +2175,13 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2209,7 +2232,7 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
